--- a/MAJSushiConfig/ig/FRAttesterLMCDAFHIR.xlsx
+++ b/MAJSushiConfig/ig/FRAttesterLMCDAFHIR.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/ConceptMap/FRAttesterLMCDAFHIR</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/ConceptMap/FRAttesterLMCDAFHIR</t>
   </si>
   <si>
     <t>Version</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:25:17+00:00</t>
+    <t>2026-09-07T11:26:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,7 +108,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMAttester</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMAttester|0.1.0</t>
   </si>
   <si>
     <t/>

--- a/MAJSushiConfig/ig/FRAttesterLMCDAFHIR.xlsx
+++ b/MAJSushiConfig/ig/FRAttesterLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="45">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T11:26:50+00:00</t>
+    <t>2026-09-07T11:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -406,7 +406,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -483,19 +483,6 @@
         <v>40</v>
       </c>
       <c r="E5" s="2"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="E6" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -504,7 +491,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -580,19 +567,6 @@
       </c>
       <c r="E5" s="2"/>
     </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="E6" s="2"/>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
